--- a/3_meta-analysis/data/sheets_for_analysis/xlsx/pivot_shift_1.xlsx
+++ b/3_meta-analysis/data/sheets_for_analysis/xlsx/pivot_shift_1.xlsx
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J2" t="n">
         <v>25</v>
@@ -569,10 +569,10 @@
         <v>24</v>
       </c>
       <c r="R2" t="n">
-        <v>0.891</v>
+        <v>0.895</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4809545240190564</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="3">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="J3" t="n">
         <v>23.6</v>
@@ -636,10 +636,10 @@
         <v>35.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>1.014</v>
       </c>
       <c r="S3" t="n">
-        <v>0.414208434789757</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="4">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J4" t="n">
         <v>28.5</v>
@@ -703,10 +703,10 @@
         <v>36</v>
       </c>
       <c r="R4" t="n">
-        <v>0.228</v>
+        <v>0.252</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7576272832434757</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="5">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>62.5</v>
       </c>
       <c r="G5" t="n">
-        <v>62</v>
+        <v>62.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
         <v>27.9</v>
@@ -770,10 +770,10 @@
         <v>29.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0.786</v>
+        <v>0.804</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6962652073452096</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="6">
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="I6" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="J6" t="n">
         <v>28.2</v>
@@ -837,10 +837,10 @@
         <v>191.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.584</v>
+        <v>1.586</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3476046147450453</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="7">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G7" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J7" t="n">
         <v>27</v>
@@ -904,10 +904,10 @@
         <v>6.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0.246</v>
+        <v>0.259</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5317803203448757</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="8">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G8" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J8" t="n">
         <v>25.8</v>
@@ -971,10 +971,10 @@
         <v>36</v>
       </c>
       <c r="R8" t="n">
-        <v>0.211</v>
+        <v>0.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8138961239524336</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="9">
@@ -1000,16 +1000,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
         <v>25.2</v>
@@ -1038,10 +1038,10 @@
         <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>0.612</v>
+        <v>0.625</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5763183643984088</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="G10" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7487363091276265</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="11">
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="G11" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="J11" t="n">
         <v>29</v>
@@ -1172,10 +1172,10 @@
         <v>24.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0.243</v>
+        <v>0.247</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5692611831545604</v>
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1201,16 +1201,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="G12" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>32.7</v>
@@ -1238,11 +1238,11 @@
       <c r="Q12" t="n">
         <v>24</v>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R12" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="13">
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J13" t="n">
         <v>22.3</v>
@@ -1306,10 +1306,10 @@
         <v>81</v>
       </c>
       <c r="R13" t="n">
-        <v>0.661</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6169266209189352</v>
+        <v>0.596</v>
       </c>
     </row>
     <row r="14">
@@ -1335,16 +1335,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="G14" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>1.075</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8455308868516602</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="15">
@@ -1402,16 +1402,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
         <v>29.9</v>
@@ -1443,7 +1443,7 @@
         <v>0.846</v>
       </c>
       <c r="S15" t="n">
-        <v>1.080662837258767</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="16">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>32</v>
@@ -1507,10 +1507,10 @@
         <v>24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.375</v>
+        <v>1.324</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6784005252999681</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="17">
@@ -1536,16 +1536,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G17" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J17" t="n">
         <v>29.8</v>
@@ -1574,10 +1574,10 @@
         <v>73.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0.365</v>
+        <v>0.389</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6635538091933179</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="18">
@@ -1603,16 +1603,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="G18" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J18" t="n">
         <v>27.1</v>
@@ -1641,10 +1641,10 @@
         <v>24</v>
       </c>
       <c r="R18" t="n">
-        <v>1.411</v>
+        <v>1.389</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5175576354608256</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="19">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="G19" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J19" t="n">
         <v>31</v>
@@ -1708,10 +1708,10 @@
         <v>24</v>
       </c>
       <c r="R19" t="n">
-        <v>0.305</v>
+        <v>0.327</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6783207557041488</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="20">
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="G20" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>28.1</v>
@@ -1775,10 +1775,10 @@
         <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.397</v>
+        <v>1.347</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8224396186997112</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="21">
@@ -1804,16 +1804,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G21" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J21" t="n">
         <v>25.8</v>
@@ -1842,10 +1842,10 @@
         <v>31.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0.424</v>
+        <v>0.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5850058480321733</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="22">
@@ -1871,16 +1871,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="G22" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J22" t="n">
         <v>25</v>
@@ -1909,10 +1909,10 @@
         <v>120</v>
       </c>
       <c r="R22" t="n">
-        <v>0.651</v>
+        <v>0.674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6048415770541352</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="23">
@@ -1938,16 +1938,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G23" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
         <v>27</v>
@@ -1976,10 +1976,10 @@
         <v>228</v>
       </c>
       <c r="R23" t="n">
-        <v>0.27</v>
+        <v>0.347</v>
       </c>
       <c r="S23" t="n">
-        <v>1.180548048024177</v>
+        <v>1.006</v>
       </c>
     </row>
     <row r="24">
@@ -2005,16 +2005,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J24" t="n">
         <v>45.5</v>
@@ -2043,10 +2043,10 @@
         <v>204</v>
       </c>
       <c r="R24" t="n">
-        <v>0.789</v>
+        <v>0.802</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6890963656627356</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="25">
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="G25" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>30.1</v>
@@ -2109,15 +2109,11 @@
       <c r="Q25" t="n">
         <v>12</v>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R25" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.498</v>
       </c>
     </row>
     <row r="26">
@@ -2143,16 +2139,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="G26" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="H26" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="I26" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="J26" t="n">
         <v>30</v>
@@ -2181,10 +2177,10 @@
         <v>34.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0.582</v>
+        <v>0.584</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3533159451400709</v>
+        <v>0.352</v>
       </c>
     </row>
   </sheetData>
